--- a/Project/Summary.xlsx
+++ b/Project/Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Education\PhD\Courses\3_DeepLearning\Assignments\Repo\202610ELC536501\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D144A3B-9781-4502-855C-E4098335F9BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F80D021-5CF5-4EBC-A9A7-9F1A40FB1D20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{04743AD6-1592-4185-AED0-955D958A5B0D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{04743AD6-1592-4185-AED0-955D958A5B0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Training" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="42">
   <si>
     <t>PTQ</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Weighted Avg</t>
   </si>
   <si>
-    <t>PTQ - Original</t>
-  </si>
-  <si>
     <t>PTQ - INT8</t>
   </si>
   <si>
@@ -99,6 +96,75 @@
   </si>
   <si>
     <t>QAT - INT64</t>
+  </si>
+  <si>
+    <t>Original</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Denoising Autoencoder</t>
+  </si>
+  <si>
+    <t>MAC Operations</t>
+  </si>
+  <si>
+    <t>4.83 million</t>
+  </si>
+  <si>
+    <t>2.96 million</t>
+  </si>
+  <si>
+    <t>Float32 Flash Size</t>
+  </si>
+  <si>
+    <t>181.53 KB</t>
+  </si>
+  <si>
+    <t>201.87 KB</t>
+  </si>
+  <si>
+    <t>INT8 Flash Size</t>
+  </si>
+  <si>
+    <t>55.84 KB</t>
+  </si>
+  <si>
+    <t>54.63 KB</t>
+  </si>
+  <si>
+    <t>Compression Ratio</t>
+  </si>
+  <si>
+    <t>3.3x</t>
+  </si>
+  <si>
+    <t>3.7x</t>
+  </si>
+  <si>
+    <t>Estimated SRAM</t>
+  </si>
+  <si>
+    <t>119.18 KB</t>
+  </si>
+  <si>
+    <t>76.41 KB</t>
+  </si>
+  <si>
+    <t>Classifier (1D-CNN)</t>
+  </si>
+  <si>
+    <t>Est. Latency (128 MHz)</t>
+  </si>
+  <si>
+    <t>92 –112 ms</t>
+  </si>
+  <si>
+    <t>50 – 70 ms</t>
   </si>
 </sst>
 </file>
@@ -175,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -188,8 +254,20 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -352,8 +430,8 @@
     <xdr:to>
       <xdr:col>20</xdr:col>
       <xdr:colOff>19505</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>121168</xdr:rowOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>260810</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -750,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4616392E-C854-4968-9DC9-68B10CEE3DF5}">
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:AA76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
@@ -758,30 +836,33 @@
     <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" customWidth="1"/>
+    <col min="11" max="11" width="7.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" customWidth="1"/>
     <col min="13" max="13" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" customWidth="1"/>
+    <col min="27" max="27" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
+      <c r="A9" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
       <c r="F9">
         <v>70.92</v>
       </c>
@@ -907,23 +988,23 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
+      <c r="A20" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
       <c r="F20">
         <v>70.92</v>
       </c>
-      <c r="I20" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
+      <c r="I20" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
       <c r="N20">
         <v>69.5</v>
       </c>
@@ -1153,23 +1234,23 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
+      <c r="A30" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
       <c r="F30">
         <v>70.92</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
+      <c r="I30" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
@@ -1399,23 +1480,23 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="6"/>
+      <c r="A40" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
       <c r="F40">
         <v>70.92</v>
       </c>
-      <c r="I40" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6"/>
+      <c r="I40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
       <c r="N40">
         <v>68.790000000000006</v>
       </c>
@@ -1644,29 +1725,38 @@
         <v>282</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
-      <c r="E50" s="6"/>
+    <row r="50" spans="1:27" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
       <c r="F50">
         <v>70.92</v>
       </c>
-      <c r="I50" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
+      <c r="I50" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
       <c r="N50">
         <v>68.790000000000006</v>
       </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Y50" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z50" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA50" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1" t="s">
         <v>1</v>
@@ -1693,8 +1783,11 @@
       <c r="M51" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Y51" s="8"/>
+      <c r="Z51" s="8"/>
+      <c r="AA51" s="8"/>
+    </row>
+    <row r="52" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>5</v>
       </c>
@@ -1725,8 +1818,17 @@
       <c r="M52" s="3">
         <v>40</v>
       </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Y52" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z52" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA52" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
@@ -1757,8 +1859,17 @@
       <c r="M53" s="3">
         <v>180</v>
       </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Y53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z53" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA53" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>7</v>
       </c>
@@ -1789,8 +1900,17 @@
       <c r="M54" s="3">
         <v>62</v>
       </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Y54" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="Z54" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA54" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -1801,8 +1921,17 @@
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Y55" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z55" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA55" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>8</v>
       </c>
@@ -1825,8 +1954,17 @@
       <c r="M56" s="3">
         <v>282</v>
       </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Y56" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z56" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA56" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>9</v>
       </c>
@@ -1857,8 +1995,17 @@
       <c r="M57" s="3">
         <v>282</v>
       </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="Y57" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z57" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA57" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>10</v>
       </c>
@@ -1890,8 +2037,151 @@
         <v>282</v>
       </c>
     </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="I62" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="I63" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="J63" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="K63" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="L63" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="I64" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J64" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="K64" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="L64" s="3">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="65" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I65" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J65" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="K65" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="L65" s="3">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="66" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I66" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0.68</v>
+      </c>
+      <c r="K66" s="3">
+        <v>0.43</v>
+      </c>
+      <c r="L66" s="3">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="72" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I72" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I73" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0.18</v>
+      </c>
+      <c r="K73" s="3">
+        <v>0.65</v>
+      </c>
+      <c r="L73" s="3">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="74" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I74" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J74" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="K74" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="L74" s="3">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="75" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I75" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J75" s="3">
+        <v>0.62</v>
+      </c>
+      <c r="K75" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="L75" s="3">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="76" spans="9:12" x14ac:dyDescent="0.25">
+      <c r="I76" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J76" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="K76" s="3">
+        <v>0.44</v>
+      </c>
+      <c r="L76" s="3">
+        <v>0.44</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="13">
+    <mergeCell ref="Y50:Y51"/>
+    <mergeCell ref="Z50:Z51"/>
+    <mergeCell ref="AA50:AA51"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="I20:M20"/>
     <mergeCell ref="I30:M30"/>
